--- a/Doc/nPM1300 Design/NPM1300 Checklist design V1.0.0.xlsx
+++ b/Doc/nPM1300 Design/NPM1300 Checklist design V1.0.0.xlsx
@@ -1054,7 +1054,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1173,9 +1173,6 @@
     </xf>
     <xf fontId="6" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="7" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1986,7 +1983,9 @@
         <v>29</v>
       </c>
       <c r="J5" s="32"/>
-      <c r="K5" s="33"/>
+      <c r="K5" s="33" t="s">
+        <v>3</v>
+      </c>
       <c r="L5" s="34"/>
     </row>
     <row r="6" ht="58">
@@ -2674,7 +2673,7 @@
       <c r="J25" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="K25" s="41" t="s">
+      <c r="K25" s="33" t="s">
         <v>3</v>
       </c>
       <c r="L25" s="34"/>
@@ -2707,7 +2706,7 @@
         <v>117</v>
       </c>
       <c r="J26" s="32"/>
-      <c r="K26" s="41" t="s">
+      <c r="K26" s="33" t="s">
         <v>3</v>
       </c>
       <c r="L26" s="34"/>
@@ -2740,7 +2739,7 @@
         <v>121</v>
       </c>
       <c r="J27" s="32"/>
-      <c r="K27" s="41" t="s">
+      <c r="K27" s="33" t="s">
         <v>3</v>
       </c>
       <c r="L27" s="34"/>
@@ -2773,10 +2772,10 @@
         <v>125</v>
       </c>
       <c r="J28" s="32"/>
-      <c r="K28" s="41" t="s">
+      <c r="K28" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="L28" s="42"/>
+      <c r="L28" s="41"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="28">
@@ -2806,7 +2805,7 @@
         <v>125</v>
       </c>
       <c r="J29" s="32"/>
-      <c r="K29" s="41" t="s">
+      <c r="K29" s="33" t="s">
         <v>3</v>
       </c>
       <c r="L29" s="34"/>
@@ -2839,7 +2838,7 @@
         <v>125</v>
       </c>
       <c r="J30" s="32"/>
-      <c r="K30" s="41" t="s">
+      <c r="K30" s="33" t="s">
         <v>3</v>
       </c>
       <c r="L30" s="34"/>
@@ -2874,7 +2873,7 @@
       <c r="J31" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="K31" s="41" t="s">
+      <c r="K31" s="33" t="s">
         <v>3</v>
       </c>
       <c r="L31" s="34"/>
@@ -2909,7 +2908,7 @@
       <c r="J32" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="K32" s="41" t="s">
+      <c r="K32" s="33" t="s">
         <v>3</v>
       </c>
       <c r="L32" s="34" t="s">
@@ -2946,7 +2945,7 @@
       <c r="J33" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="K33" s="41" t="s">
+      <c r="K33" s="33" t="s">
         <v>3</v>
       </c>
       <c r="L33" s="34"/>
@@ -2981,7 +2980,7 @@
       <c r="J34" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="K34" s="41" t="s">
+      <c r="K34" s="33" t="s">
         <v>3</v>
       </c>
       <c r="L34" s="34" t="s">
@@ -3018,7 +3017,7 @@
       <c r="J35" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="K35" s="41" t="s">
+      <c r="K35" s="33" t="s">
         <v>3</v>
       </c>
       <c r="L35" s="34"/>
@@ -3043,14 +3042,14 @@
       <c r="G36" s="29">
         <v>0</v>
       </c>
-      <c r="H36" s="43" t="s">
+      <c r="H36" s="42" t="s">
         <v>155</v>
       </c>
       <c r="I36" s="37" t="s">
         <v>156</v>
       </c>
       <c r="J36" s="32"/>
-      <c r="K36" s="41" t="s">
+      <c r="K36" s="33" t="s">
         <v>3</v>
       </c>
       <c r="L36" s="34"/>
@@ -3070,7 +3069,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{00AC00B9-0092-44B3-8C58-00DB0045005D}">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{00F700CC-00C4-4071-94C2-0052001F00D3}">
             <xm:f>"NOK"</xm:f>
             <x14:dxf>
               <fill>
@@ -3084,7 +3083,7 @@
           <xm:sqref>K4:K9 K11:K36 L10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{0090001F-0085-4B8F-88AA-00C600C50062}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{00AC004A-00F8-4C44-890A-000600820036}">
             <xm:f>"OK"</xm:f>
             <x14:dxf>
               <fill>
@@ -3107,7 +3106,7 @@
           <xm:sqref>K4:K9 K11:K36 L10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{00F00024-00C6-4013-8148-0040009E007B}">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{0024004A-0089-4D9A-BF20-00F9003C00CA}">
             <xm:f>"NOK"</xm:f>
             <x14:dxf>
               <fill>
@@ -3121,7 +3120,7 @@
           <xm:sqref>K10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{00980073-00E7-4D3A-BB0C-00DF00C300EC}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{00540086-00A2-4981-A2B9-00D300BA0017}">
             <xm:f>"OK"</xm:f>
             <x14:dxf>
               <fill>
@@ -3147,13 +3146,13 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{0042008C-005A-43E0-8389-00A1004E002C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00D3002A-00A6-419D-8BE6-00DA00D900C1}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$K$1:$K$2</xm:f>
           </x14:formula1>
           <xm:sqref>K4:K9 K11:K36 L10</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{0053003F-0030-40D7-987A-00110052001F}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00F2001A-000E-4028-9C3B-00C300300029}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$K$1:$K$2</xm:f>
           </x14:formula1>
@@ -3204,10 +3203,10 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="44" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="12" t="s">
@@ -3777,7 +3776,7 @@
         <v>179</v>
       </c>
       <c r="G28" s="33"/>
-      <c r="H28" s="42"/>
+      <c r="H28" s="41"/>
     </row>
     <row r="29">
       <c r="A29" s="28">
@@ -3946,7 +3945,7 @@
       <c r="C36" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="D36" s="43" t="s">
+      <c r="D36" s="42" t="s">
         <v>155</v>
       </c>
       <c r="E36" s="37" t="s">
@@ -3972,7 +3971,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{003200D2-004F-4646-8A6B-002B008000CE}">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{00B40008-0036-439D-8CCA-00EC0013004A}">
             <xm:f>"NOK"</xm:f>
             <x14:dxf>
               <fill>
@@ -3986,7 +3985,7 @@
           <xm:sqref>G4:G36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{00C500E5-0021-4499-8DCA-00AE00B10012}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{003F00C7-0005-4C7D-9756-007F00DB00F1}">
             <xm:f>"OK"</xm:f>
             <x14:dxf>
               <fill>
@@ -4012,7 +4011,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00000093-0031-45E0-92AC-00A500860070}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{0070004F-009C-4E47-AFDD-007200A100DE}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$1:$G$2</xm:f>
           </x14:formula1>
@@ -4045,10 +4044,10 @@
       </c>
     </row>
     <row r="3" ht="15">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="46" t="s">
         <v>187</v>
       </c>
       <c r="C3" s="16" t="s">
@@ -4059,142 +4058,142 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="47" t="s">
         <v>188</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="49" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="49"/>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="49"/>
     </row>
     <row r="7">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="49"/>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="49" t="s">
         <v>194</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="49" t="s">
         <v>195</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="52"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="51"/>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="49" t="s">
         <v>196</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="49"/>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="49" t="s">
         <v>199</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="49"/>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="49"/>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="52"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="51"/>
     </row>
     <row r="13" ht="29">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="52" t="s">
         <v>203</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="52"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="51"/>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="49" t="s">
         <v>204</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="52"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="51"/>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="49" t="s">
         <v>205</v>
       </c>
-      <c r="B15" s="50" t="s">
+      <c r="B15" s="49" t="s">
         <v>206</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="52"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="51"/>
     </row>
     <row r="20">
-      <c r="A20" s="54"/>
+      <c r="A20" s="53"/>
     </row>
     <row r="21">
-      <c r="A21" s="54"/>
+      <c r="A21" s="53"/>
     </row>
     <row r="22">
-      <c r="A22" s="54"/>
+      <c r="A22" s="53"/>
     </row>
     <row r="23">
-      <c r="A23" s="54"/>
+      <c r="A23" s="53"/>
     </row>
     <row r="24">
-      <c r="A24" s="54"/>
+      <c r="A24" s="53"/>
     </row>
     <row r="25">
-      <c r="A25" s="54"/>
+      <c r="A25" s="53"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:D15">
@@ -4210,7 +4209,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{00A300AE-00EE-4CD5-958A-00AF00A40083}">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{006B00E8-00F8-4320-9424-00DE001200CD}">
             <xm:f>"NOK"</xm:f>
             <x14:dxf>
               <fill>
@@ -4224,7 +4223,7 @@
           <xm:sqref>C4:C15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{003B00E7-0058-4828-8089-008500D9006E}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{00FC005C-0058-4B0B-BFFB-004F00D4000B}">
             <xm:f>"OK"</xm:f>
             <x14:dxf>
               <fill>
@@ -4250,7 +4249,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00270068-006D-48B7-BA7B-008800950009}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00BF00F0-0035-4DE1-B7C5-006E00DB0033}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$C$1:$C$2</xm:f>
           </x14:formula1>
@@ -4273,10 +4272,10 @@
   <sheetData>
     <row r="2" ht="15"/>
     <row r="3" ht="15">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="54" t="s">
         <v>207</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="55" t="s">
         <v>208</v>
       </c>
       <c r="C3" s="16" t="s">
@@ -4284,60 +4283,60 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="56" t="s">
         <v>210</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="47" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="59"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
     </row>
     <row r="6">
-      <c r="A6" s="59"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
+      <c r="A6" s="58"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
     </row>
     <row r="7">
-      <c r="A7" s="59"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
+      <c r="A7" s="58"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
     </row>
     <row r="8">
-      <c r="A8" s="60"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
     </row>
     <row r="9">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
     </row>
     <row r="10">
-      <c r="A10" s="60"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
     </row>
     <row r="11">
-      <c r="A11" s="52"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
+      <c r="A11" s="51"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
     </row>
     <row r="12">
-      <c r="A12" s="52"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
     </row>
     <row r="13">
-      <c r="A13" s="52"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
